--- a/examples/sample_report.xlsx
+++ b/examples/sample_report.xlsx
@@ -1110,7 +1110,7 @@
               <color rgb="00D9A521"/>
               <sz val="10"/>
             </rPr>
-            <t>v0.1.0</t>
+            <t>v0.1.1</t>
           </r>
         </is>
       </c>
